--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0225.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0225.xlsx
@@ -3436,7 +3436,7 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>Triệu hồi &lt;color=#2c9366&gt;&lt;te href=800024&gt;Feilian Shocks&lt;/te&gt;&lt;/color&gt;.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Summon Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800027&gt;Vũ Khí Triệu Hồi&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3502,8 +3502,8 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Bắn &lt;color=#917701&gt;&lt;te href=800016&gt;Glittering Rays&lt;/te&gt;&lt;/color&gt;.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Beam Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>Bắn &lt;color=#917701&gt;&lt;te href=800016&gt;Tia Lấp Lánh&lt;/te&gt;&lt;/color&gt;.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800028&gt;Vũ Khí Tia&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3569,8 +3569,8 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Phun liên tục &lt;color=#9c5884&gt;&lt;te href=800023&gt;Rampant Fire&lt;/te&gt;&lt;/color&gt; về phía trước.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Morph Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>Phun liên tục &lt;color=#9c5884&gt;&lt;te href=800023&gt;Lửa Dữ Dội&lt;/te&gt;&lt;/color&gt; về phía trước.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Biến Hình Vũ Khí&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -3636,8 +3636,8 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Giải phóng &lt;color=#be6245&gt;&lt;te href=800025&gt;Explosive Omens&lt;/te&gt;&lt;/color&gt; theo mọi hướng.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Morph Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+          <t>Giải phóng &lt;color=#be6245&gt;&lt;te href=800025&gt;Điềm Báo Bùng Nổ&lt;/te&gt;&lt;/color&gt; theo mọi hướng.
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800029&gt;Biến Hình Vũ Khí&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm vào bất kỳ đâu PC=Nhấp bất kỳ đâu Gamepad=Nhấn bất kỳ nút nào} để đóng</t>
+          <t>Nhấn bất kỳ đâu để đóng</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>R?i ?i.</t>
+          <t>Rời đi.</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Mở khóa Trang trí Quán cà phê. Bạn có thể sử dụng tài nguyên để nâng cấp Shashou Cafe.</t>
+          <t>Mở khóa Trang trí Quán cà phê. Bạn có thể dùng tài nguyên để nâng cấp Shashou Cafe.</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Số lượng Cộng Hưởng Giả cần thăng cấp: {0}/{1}</t>
+          <t>Resonator Ascension Required Amount {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>&lt;\color=#ffd12f&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>&lt;color=#c25757&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Tệp ngoại hình của Rover chưa được tải. Tải ngay?</t>
+          <t>Tệp ngoại hình của Vận Mệnh Giả chưa được tải. Tải ngay?</t>
         </is>
       </c>
     </row>
@@ -22275,7 +22275,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Tệp ngoại hình của Rover đã tải xong. Hãy vào Cài đặt để thay đổi.</t>
+          <t>Tệp ngoại hình của Vận Mệnh Giả đã tải xong. Hãy vào Cài đặt để thay đổi.</t>
         </is>
       </c>
     </row>
